--- a/data/output/evaluasi_35.xlsx
+++ b/data/output/evaluasi_35.xlsx
@@ -8,18 +8,36 @@
   </bookViews>
   <sheets>
     <sheet name="3500" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="3578" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3501" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3505" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3515" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3516" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="3518" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3519" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="3526" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="3579" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="3506" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="3525" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="3529" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="3501" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3505" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3511" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3513" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3519" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3521" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3522" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3524" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3527" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3528" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3579" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="3503" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="3504" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="3529" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="3571" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="3573" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="3575" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="3576" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="3578" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="3506" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="3520" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="3517" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="3577" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="3572" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="3507" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="3514" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="3515" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="3523" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="3509" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="3574" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,20 +501,188 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9725322811957005</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.5471170083739035</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="D3" t="n">
+        <v>0.9775280493066376</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-12.34292265598814</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.542837707877791</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.432416183003291</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.161541046747152</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25 vs implisit_y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.87819713457258</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -548,85 +734,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3579</v>
+        <v>3527</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Batu</t>
+          <t>Kabupaten Sampang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.41389184471282</v>
+        <v>-1.366925299628231</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3579</v>
+        <v>3527</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Batu</t>
+          <t>Kabupaten Sampang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.41389184471282</v>
+        <v>0.009482920347081546</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3579</v>
+        <v>3527</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Batu</t>
+          <t>Kabupaten Sampang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1437028100483435</v>
+        <v>-0.08458359543152952</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -641,7 +827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,57 +864,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3506</v>
+        <v>3528</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Kediri</t>
+          <t>Kabupaten Pamekasan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.755981383579781</v>
+        <v>-2.015928849003041</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3506</v>
+        <v>3528</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Kediri</t>
+          <t>Kabupaten Pamekasan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.477646380513893</v>
+        <v>0.1980797049062209</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3528</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pamekasan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.615207169830335</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3528</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pamekasan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.959295495175528</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -780,29 +1022,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3525</v>
+        <v>3579</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Gresik</t>
+          <t>Kota Batu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5311106444477642</v>
+        <v>-2.676264804505277</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -817,6 +1059,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.837070620613945</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.48907101414677</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Trenggalek</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.84705582009451</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -854,6 +1226,80 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tulungagung</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3514231250581711</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>3529</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -863,20 +1309,484 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.500438927171373</v>
+        <v>0.1835830511307743</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3529</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumenep</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9105738940516522</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3529</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumenep</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.648968413675984</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3529</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumenep</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.660424462338403</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3571</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Kediri</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.465689216561392</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3573</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.342730028038388</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3575</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1410540449451309</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3575</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.868128244543852</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3575</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.125596950662656</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3576</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Mojokerto</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1094132675111372</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3576</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Mojokerto</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.1229940416974763</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -891,6 +1801,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.249751582984942</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01586238622911746</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3948206214006234</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pacitan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.528062006951281</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02355619913535991</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3578</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3113154875621609</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -928,85 +2098,817 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3578</v>
+        <v>3506</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Surabaya</t>
+          <t>Kabupaten Kediri</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.07034828564577621</v>
+        <v>0.67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25_ril vs q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3578</v>
+        <v>3506</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Surabaya</t>
+          <t>Kabupaten Kediri</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2649123186753021</v>
+        <v>-1.712915761964397</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3578</v>
+        <v>3506</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Surabaya</t>
+          <t>Kabupaten Kediri</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03993705224309031</v>
+        <v>0.210084478941143</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pkrt_q1-25_ril vs sog_q_pkrt_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Magetan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5320394940341483</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Magetan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.399507618612341</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3517</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Jombang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.983188854231177</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3517</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Jombang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.296018668750827</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3577</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Madiun</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.05122350933416904</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3577</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Madiun</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05370276187469941</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3572</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Blitar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10.03389150303147</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4317288203621154</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.178975725176303</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.966455812564388</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3514</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasuruan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5872946547773843</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sidoarjo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.540934262164721</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3523</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tuban</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.354215508338437</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1058,85 +2960,261 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3501</v>
+        <v>3505</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pacitan</t>
+          <t>Kabupaten Blitar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.028229164979268</v>
+        <v>-1.575770879384187</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3501</v>
+        <v>3505</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Pacitan</t>
+          <t>Kabupaten Blitar</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.028229164979268</v>
+        <v>-0.0739999999999869</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3501</v>
+        <v>3505</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Pacitan</t>
+          <t>Kabupaten Blitar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.07579969062419038</v>
+        <v>-0.7173295439158024</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.3128632571328843</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Jember</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.875019616758443</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3574</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.782114730925002</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1151,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,113 +3266,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3505</v>
+        <v>3511</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Blitar</t>
+          <t>Kabupaten Bondowoso</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.565569770093862</v>
+        <v>-2.617888276248488</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3505</v>
+        <v>3511</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Blitar</t>
+          <t>Kabupaten Bondowoso</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.565569770093862</v>
+        <v>1.273241382306653</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3505</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kabupaten Blitar</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1380931428353813</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3505</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Blitar</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.3988153254678744</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1309,7 +3331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1346,85 +3368,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Sidoarjo</t>
+          <t>Kabupaten Probolinggo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.8821182299696615</v>
+        <v>-2.906417381224891</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3515</v>
+        <v>3513</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Sidoarjo</t>
+          <t>Kabupaten Probolinggo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.8821182299696615</v>
+        <v>0.03216380756288918</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3515</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kabupaten Sidoarjo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.0382546094209019</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1439,7 +3433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1476,85 +3470,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3516</v>
+        <v>3519</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Mojokerto</t>
+          <t>Kabupaten Madiun</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.477395750315152</v>
+        <v>7.839729357529861</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3516</v>
+        <v>3519</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Mojokerto</t>
+          <t>Kabupaten Madiun</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.477395750315152</v>
+        <v>1.869305902842486</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3516</v>
+        <v>3519</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Mojokerto</t>
+          <t>Kabupaten Madiun</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04402196117745583</v>
+        <v>-0.0225236889521508</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3519</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Madiun</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.086047127891722</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3519</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Madiun</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.168734116489675</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1569,7 +3619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,197 +3656,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3518</v>
+        <v>3521</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Nganjuk</t>
+          <t>Kabupaten Ngawi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3.81375565307439</v>
+        <v>12.04941975488347</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3518</v>
+        <v>3521</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Nganjuk</t>
+          <t>Kabupaten Ngawi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3.81375565307439</v>
+        <v>0.5328610770662537</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3518</v>
+        <v>3521</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Nganjuk</t>
+          <t>Kabupaten Ngawi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.303843559347777</v>
+        <v>10.57757725868457</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3518</v>
+        <v>3521</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Nganjuk</t>
+          <t>Kabupaten Ngawi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.448651085646544</v>
+        <v>0.5660521968920931</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3518</v>
+        <v>3521</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Nganjuk</t>
+          <t>Kabupaten Ngawi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.522541838069258</v>
+        <v>0.8817633317823605</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3518</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Nganjuk</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2352438361108746</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>3518</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Nganjuk</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.2466277446826685</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1811,7 +3805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1848,169 +3842,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3519</v>
+        <v>3522</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Madiun</t>
+          <t>Kabupaten Bojonegoro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.783304531247262</v>
+        <v>-0.6307445997666471</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3519</v>
+        <v>3522</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Madiun</t>
+          <t>Kabupaten Bojonegoro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.783304531247262</v>
+        <v>-3.90090101771345</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3519</v>
+        <v>3522</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Madiun</t>
+          <t>Kabupaten Bojonegoro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.106517243086972</v>
+        <v>4.867978332742555</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3519</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Madiun</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5987624652409422</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3519</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Madiun</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1259532777089458</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3519</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Madiun</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.09405586824963456</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2025,7 +3935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2062,85 +3972,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3526</v>
+        <v>3524</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bangkalan</t>
+          <t>Kabupaten Lamongan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.483372646762986</v>
+        <v>-3.031824840752845</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3526</v>
+        <v>3524</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bangkalan</t>
+          <t>Kabupaten Lamongan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.483372646762986</v>
+        <v>1.446297482930753</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3526</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kabupaten Bangkalan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1536334824590105</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_35.xlsx
+++ b/data/output/evaluasi_35.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
